--- a/design/tables/ChallengePerk.xlsx
+++ b/design/tables/ChallengePerk.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengePerk" sheetId="1" r:id="R3e84e1f64fbc478d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengePerk" sheetId="1" r:id="R57b128085e1b4696"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -475,7 +475,7 @@
         <x:v>perk.S01.desc</x:v>
       </x:c>
       <x:c r="G6" s="6" t="str">
-        <x:v>sprout</x:v>
+        <x:v>perk_S01</x:v>
       </x:c>
       <x:c r="H6" s="6" t="str">
         <x:v>{"every":3,"shots":3,"ratio":0.7}</x:v>
@@ -506,7 +506,7 @@
         <x:v>perk.S02.desc</x:v>
       </x:c>
       <x:c r="G7" s="6" t="str">
-        <x:v>frost</x:v>
+        <x:v>perk_S02</x:v>
       </x:c>
       <x:c r="H7" s="6" t="str">
         <x:v>{"radius":80,"count":2,"seconds":1.5}</x:v>
@@ -537,7 +537,7 @@
         <x:v>perk.S03.desc</x:v>
       </x:c>
       <x:c r="G8" s="6" t="str">
-        <x:v>bloom</x:v>
+        <x:v>perk_S03</x:v>
       </x:c>
       <x:c r="H8" s="6" t="str">
         <x:v>{"every":3,"delay":0.35,"ratio":0.8}</x:v>
@@ -568,7 +568,7 @@
         <x:v>perk.S04.desc</x:v>
       </x:c>
       <x:c r="G9" s="6" t="str">
-        <x:v>scope</x:v>
+        <x:v>perk_S04</x:v>
       </x:c>
       <x:c r="H9" s="6" t="str">
         <x:v>{"ratio":0.6}</x:v>
@@ -599,7 +599,7 @@
         <x:v>perk.S05.desc</x:v>
       </x:c>
       <x:c r="G10" s="6" t="str">
-        <x:v>spark</x:v>
+        <x:v>perk_S05</x:v>
       </x:c>
       <x:c r="H10" s="6" t="str">
         <x:v>{"every":3,"ratio":0.6}</x:v>
@@ -630,7 +630,7 @@
         <x:v>perk.S06.desc</x:v>
       </x:c>
       <x:c r="G11" s="6" t="str">
-        <x:v>ember</x:v>
+        <x:v>perk_S06</x:v>
       </x:c>
       <x:c r="H11" s="6" t="str">
         <x:v>{"radius":65,"ratio":2}</x:v>
@@ -661,7 +661,7 @@
         <x:v>perk.S07.desc</x:v>
       </x:c>
       <x:c r="G12" s="6" t="str">
-        <x:v>mint</x:v>
+        <x:v>perk_S07</x:v>
       </x:c>
       <x:c r="H12" s="6" t="str">
         <x:v>{"radius":100,"count":2,"seconds":2,"generations":3}</x:v>
@@ -692,7 +692,7 @@
         <x:v>perk.S08.desc</x:v>
       </x:c>
       <x:c r="G13" s="6" t="str">
-        <x:v>fan</x:v>
+        <x:v>perk_S08</x:v>
       </x:c>
       <x:c r="H13" s="6" t="str">
         <x:v>{"radius":65,"ratio":0.6}</x:v>
@@ -721,7 +721,7 @@
         <x:v>perk.G01.desc</x:v>
       </x:c>
       <x:c r="G14" s="6" t="str">
-        <x:v>scope</x:v>
+        <x:v>perk_G01</x:v>
       </x:c>
       <x:c r="H14" s="6" t="str">
         <x:v>{"seconds":6,"rate":-0.35}</x:v>
@@ -750,7 +750,7 @@
         <x:v>perk.G02.desc</x:v>
       </x:c>
       <x:c r="G15" s="6" t="str">
-        <x:v>scope</x:v>
+        <x:v>perk_G02</x:v>
       </x:c>
       <x:c r="H15" s="6" t="str">
         <x:v>{"radius":90,"damage":0.25}</x:v>
@@ -779,7 +779,7 @@
         <x:v>perk.G03.desc</x:v>
       </x:c>
       <x:c r="G16" s="6" t="str">
-        <x:v>scope</x:v>
+        <x:v>perk_G03</x:v>
       </x:c>
       <x:c r="H16" s="6" t="str">
         <x:v>{"radius":90,"damage":0.5,"range":-0.1}</x:v>
@@ -808,7 +808,7 @@
         <x:v>perk.G04.desc</x:v>
       </x:c>
       <x:c r="G17" s="6" t="str">
-        <x:v>scope</x:v>
+        <x:v>perk_G04</x:v>
       </x:c>
       <x:c r="H17" s="6" t="str">
         <x:v>{"step":100,"damage":0.1,"cap":0.4}</x:v>
@@ -837,7 +837,7 @@
         <x:v>perk.G05.desc</x:v>
       </x:c>
       <x:c r="G18" s="6" t="str">
-        <x:v>scope</x:v>
+        <x:v>perk_G05</x:v>
       </x:c>
       <x:c r="H18" s="6" t="str">
         <x:v>{"damage":0.25,"range":0.15}</x:v>
@@ -866,7 +866,7 @@
         <x:v>perk.G06.desc</x:v>
       </x:c>
       <x:c r="G19" s="6" t="str">
-        <x:v>scope</x:v>
+        <x:v>perk_G06</x:v>
       </x:c>
       <x:c r="H19" s="6" t="str">
         <x:v>{"damage":0.35}</x:v>
@@ -895,7 +895,7 @@
         <x:v>perk.E01.desc</x:v>
       </x:c>
       <x:c r="G20" s="6" t="str">
-        <x:v>sprout</x:v>
+        <x:v>perk_E01</x:v>
       </x:c>
       <x:c r="H20" s="6" t="str">
         <x:v>{"coins":200}</x:v>
@@ -924,7 +924,7 @@
         <x:v>perk.E02.desc</x:v>
       </x:c>
       <x:c r="G21" s="6" t="str">
-        <x:v>sprout</x:v>
+        <x:v>perk_E02</x:v>
       </x:c>
       <x:c r="H21" s="6" t="str">
         <x:v>{"waves":5,"ratio":0.15,"cap":75}</x:v>
@@ -953,7 +953,7 @@
         <x:v>perk.E03.desc</x:v>
       </x:c>
       <x:c r="G22" s="6" t="str">
-        <x:v>sprout</x:v>
+        <x:v>perk_E03</x:v>
       </x:c>
       <x:c r="H22" s="6" t="str">
         <x:v>{"charges":3}</x:v>
@@ -984,7 +984,7 @@
         <x:v>perk.E04.desc</x:v>
       </x:c>
       <x:c r="G23" s="6" t="str">
-        <x:v>sprout</x:v>
+        <x:v>perk_E04</x:v>
       </x:c>
       <x:c r="H23" s="6" t="str">
         <x:v>{"charges":2}</x:v>
@@ -1015,7 +1015,7 @@
         <x:v>perk.E05.desc</x:v>
       </x:c>
       <x:c r="G24" s="6" t="str">
-        <x:v>sprout</x:v>
+        <x:v>perk_E05</x:v>
       </x:c>
       <x:c r="H24" s="6" t="str">
         <x:v>{"coins":60,"reward":30}</x:v>
@@ -1046,7 +1046,7 @@
         <x:v>perk.E06.desc</x:v>
       </x:c>
       <x:c r="G25" s="6" t="str">
-        <x:v>sprout</x:v>
+        <x:v>perk_E06</x:v>
       </x:c>
       <x:c r="H25" s="6" t="str">
         <x:v>{"ratio":0.25}</x:v>
@@ -1075,7 +1075,7 @@
         <x:v>perk.X01.desc</x:v>
       </x:c>
       <x:c r="G26" s="6" t="str">
-        <x:v>mint</x:v>
+        <x:v>perk_X01</x:v>
       </x:c>
       <x:c r="H26" s="6" t="str">
         <x:v>{"progress":0.3}</x:v>
@@ -1104,7 +1104,7 @@
         <x:v>perk.X02.desc</x:v>
       </x:c>
       <x:c r="G27" s="6" t="str">
-        <x:v>mint</x:v>
+        <x:v>perk_X02</x:v>
       </x:c>
       <x:c r="H27" s="6" t="str">
         <x:v>{"shield":2}</x:v>
@@ -1133,7 +1133,7 @@
         <x:v>perk.X03.desc</x:v>
       </x:c>
       <x:c r="G28" s="6" t="str">
-        <x:v>mint</x:v>
+        <x:v>perk_X03</x:v>
       </x:c>
       <x:c r="H28" s="6" t="str">
         <x:v>{"count":3,"progress":0.8,"ratio":0.4,"seconds":2}</x:v>
@@ -1162,7 +1162,7 @@
         <x:v>perk.X04.desc</x:v>
       </x:c>
       <x:c r="G29" s="6" t="str">
-        <x:v>mint</x:v>
+        <x:v>perk_X04</x:v>
       </x:c>
       <x:c r="H29" s="6" t="str">
         <x:v>{"coins":100,"rate":-0.25,"seconds":4}</x:v>
@@ -1191,7 +1191,7 @@
         <x:v>perk.X05.desc</x:v>
       </x:c>
       <x:c r="G30" s="6" t="str">
-        <x:v>mint</x:v>
+        <x:v>perk_X05</x:v>
       </x:c>
       <x:c r="H30" s="6" t="str">
         <x:v>{"radius":100,"ratio":0.35}</x:v>
@@ -1222,7 +1222,7 @@
         <x:v>perk.X06.desc</x:v>
       </x:c>
       <x:c r="G31" s="6" t="str">
-        <x:v>mint</x:v>
+        <x:v>perk_X06</x:v>
       </x:c>
       <x:c r="H31" s="6" t="str">
         <x:v>{"damage":0.8}</x:v>
@@ -1251,7 +1251,7 @@
         <x:v>perk.F01.desc</x:v>
       </x:c>
       <x:c r="G32" s="6" t="str">
-        <x:v>fan</x:v>
+        <x:v>perk_F01</x:v>
       </x:c>
       <x:c r="H32" s="6" t="str">
         <x:v>{"damage":0.8,"range":0.15,"rate":0.2,"scale":1.35}</x:v>
@@ -1282,7 +1282,7 @@
         <x:v>perk.F02.desc</x:v>
       </x:c>
       <x:c r="G33" s="6" t="str">
-        <x:v>fan</x:v>
+        <x:v>perk_F02</x:v>
       </x:c>
       <x:c r="H33" s="6" t="str">
         <x:v>{"rate":-0.25,"damage":-0.1,"scale":0.8}</x:v>
@@ -1313,7 +1313,7 @@
         <x:v>perk.F03.desc</x:v>
       </x:c>
       <x:c r="G34" s="6" t="str">
-        <x:v>fan</x:v>
+        <x:v>perk_F03</x:v>
       </x:c>
       <x:c r="H34" s="6" t="str">
         <x:v>{"every":12,"limit":3,"coins":20,"damage":100,"radius":80,"ratio":0.4,"seconds":2}</x:v>
@@ -1342,7 +1342,7 @@
         <x:v>perk.F04.desc</x:v>
       </x:c>
       <x:c r="G35" s="6" t="str">
-        <x:v>fan</x:v>
+        <x:v>perk_F04</x:v>
       </x:c>
       <x:c r="H35" s="6" t="str">
         <x:v>{"every":24,"damage":100,"count":8,"cooldown":8,"speed":240,"seconds":6,"radius":24}</x:v>
@@ -1371,7 +1371,7 @@
         <x:v>perk.F05.desc</x:v>
       </x:c>
       <x:c r="G36" s="6" t="str">
-        <x:v>fan</x:v>
+        <x:v>perk_F05</x:v>
       </x:c>
       <x:c r="H36" s="6" t="str">
         <x:v>{"interval":10,"count":3,"delay":0.6,"radius":40,"damage":80}</x:v>
@@ -1400,7 +1400,7 @@
         <x:v>perk.F06.desc</x:v>
       </x:c>
       <x:c r="G37" s="6" t="str">
-        <x:v>fan</x:v>
+        <x:v>perk_F06</x:v>
       </x:c>
       <x:c r="H37" s="6" t="str">
         <x:v>{"hp":2,"reward":4}</x:v>

--- a/design/tables/ChallengePerk.xlsx
+++ b/design/tables/ChallengePerk.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengePerk" sheetId="1" r:id="R57b128085e1b4696"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengePerk" sheetId="1" r:id="R7959f54e62e740e6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -571,7 +571,7 @@
         <x:v>perk_S04</x:v>
       </x:c>
       <x:c r="H9" s="6" t="str">
-        <x:v>{"ratio":0.6}</x:v>
+        <x:v>{"ratio":0.35}</x:v>
       </x:c>
       <x:c r="I9" s="6" t="str"/>
       <x:c r="J9" s="6" t="n">
@@ -633,7 +633,7 @@
         <x:v>perk_S06</x:v>
       </x:c>
       <x:c r="H11" s="6" t="str">
-        <x:v>{"radius":65,"ratio":2}</x:v>
+        <x:v>{"radius":56,"ratio":1.2,"count":6}</x:v>
       </x:c>
       <x:c r="I11" s="6" t="str"/>
       <x:c r="J11" s="6" t="n">
@@ -811,7 +811,7 @@
         <x:v>perk_G04</x:v>
       </x:c>
       <x:c r="H17" s="6" t="str">
-        <x:v>{"step":100,"damage":0.1,"cap":0.4}</x:v>
+        <x:v>{"step":100,"damage":0.02,"cap":0.2}</x:v>
       </x:c>
       <x:c r="I17" s="6" t="str"/>
       <x:c r="J17" s="6" t="n">
@@ -1225,7 +1225,7 @@
         <x:v>perk_X06</x:v>
       </x:c>
       <x:c r="H31" s="6" t="str">
-        <x:v>{"damage":0.8}</x:v>
+        <x:v>{"damage":0.4}</x:v>
       </x:c>
       <x:c r="I31" s="6" t="str"/>
       <x:c r="J31" s="6" t="n">

--- a/design/tables/ChallengePerk.xlsx
+++ b/design/tables/ChallengePerk.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengePerk" sheetId="1" r:id="R7959f54e62e740e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengePerk" sheetId="1" r:id="Rd52a31deaf1644de"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -478,7 +478,7 @@
         <x:v>perk_S01</x:v>
       </x:c>
       <x:c r="H6" s="6" t="str">
-        <x:v>{"every":3,"shots":3,"ratio":0.7}</x:v>
+        <x:v>{"every":2,"shots":3,"ratio":0.7}</x:v>
       </x:c>
       <x:c r="I6" s="6" t="str"/>
       <x:c r="J6" s="6" t="n">
@@ -540,7 +540,7 @@
         <x:v>perk_S03</x:v>
       </x:c>
       <x:c r="H8" s="6" t="str">
-        <x:v>{"every":3,"delay":0.35,"ratio":0.8}</x:v>
+        <x:v>{"every":2,"delay":0.22,"ratio":0.9,"radiusRatio":1.45}</x:v>
       </x:c>
       <x:c r="I8" s="6" t="str"/>
       <x:c r="J8" s="6" t="n">
@@ -602,7 +602,7 @@
         <x:v>perk_S05</x:v>
       </x:c>
       <x:c r="H10" s="6" t="str">
-        <x:v>{"every":3,"ratio":0.6}</x:v>
+        <x:v>{"every":2,"ratio":0.8,"count":5}</x:v>
       </x:c>
       <x:c r="I10" s="6" t="str"/>
       <x:c r="J10" s="6" t="n">
@@ -633,7 +633,7 @@
         <x:v>perk_S06</x:v>
       </x:c>
       <x:c r="H11" s="6" t="str">
-        <x:v>{"radius":56,"ratio":1.2,"count":6}</x:v>
+        <x:v>{"radius":72,"ratio":2.1,"count":8}</x:v>
       </x:c>
       <x:c r="I11" s="6" t="str"/>
       <x:c r="J11" s="6" t="n">
@@ -695,7 +695,7 @@
         <x:v>perk_S08</x:v>
       </x:c>
       <x:c r="H13" s="6" t="str">
-        <x:v>{"radius":65,"ratio":0.6}</x:v>
+        <x:v>{"radius":80,"ratio":0.8}</x:v>
       </x:c>
       <x:c r="I13" s="6" t="str"/>
       <x:c r="J13" s="6" t="n">

--- a/design/tables/ChallengePerk.xlsx
+++ b/design/tables/ChallengePerk.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengePerk" sheetId="1" r:id="Rd52a31deaf1644de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengePerk" sheetId="1" r:id="R061e13ea59494f04"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -482,7 +482,7 @@
       </x:c>
       <x:c r="I6" s="6" t="str"/>
       <x:c r="J6" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K6" s="6" t="str"/>
     </x:row>
@@ -513,7 +513,7 @@
       </x:c>
       <x:c r="I7" s="6" t="str"/>
       <x:c r="J7" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K7" s="6" t="str"/>
     </x:row>
@@ -544,7 +544,7 @@
       </x:c>
       <x:c r="I8" s="6" t="str"/>
       <x:c r="J8" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K8" s="6" t="str"/>
     </x:row>
@@ -575,7 +575,7 @@
       </x:c>
       <x:c r="I9" s="6" t="str"/>
       <x:c r="J9" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K9" s="6" t="str"/>
     </x:row>
@@ -606,7 +606,7 @@
       </x:c>
       <x:c r="I10" s="6" t="str"/>
       <x:c r="J10" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K10" s="6" t="str"/>
     </x:row>
@@ -637,7 +637,7 @@
       </x:c>
       <x:c r="I11" s="6" t="str"/>
       <x:c r="J11" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K11" s="6" t="str"/>
     </x:row>
@@ -668,7 +668,7 @@
       </x:c>
       <x:c r="I12" s="6" t="str"/>
       <x:c r="J12" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K12" s="6" t="str"/>
     </x:row>
@@ -699,7 +699,7 @@
       </x:c>
       <x:c r="I13" s="6" t="str"/>
       <x:c r="J13" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K13" s="6" t="str"/>
     </x:row>
@@ -728,7 +728,7 @@
       </x:c>
       <x:c r="I14" s="6" t="str"/>
       <x:c r="J14" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K14" s="6" t="str"/>
     </x:row>
@@ -757,7 +757,7 @@
       </x:c>
       <x:c r="I15" s="6" t="str"/>
       <x:c r="J15" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K15" s="6" t="str"/>
     </x:row>
@@ -786,7 +786,7 @@
       </x:c>
       <x:c r="I16" s="6" t="str"/>
       <x:c r="J16" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K16" s="6" t="str"/>
     </x:row>
@@ -815,7 +815,7 @@
       </x:c>
       <x:c r="I17" s="6" t="str"/>
       <x:c r="J17" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K17" s="6" t="str"/>
     </x:row>
@@ -844,7 +844,7 @@
       </x:c>
       <x:c r="I18" s="6" t="str"/>
       <x:c r="J18" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K18" s="6" t="str"/>
     </x:row>
@@ -873,7 +873,7 @@
       </x:c>
       <x:c r="I19" s="6" t="str"/>
       <x:c r="J19" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K19" s="6" t="str"/>
     </x:row>
@@ -902,7 +902,7 @@
       </x:c>
       <x:c r="I20" s="6" t="str"/>
       <x:c r="J20" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K20" s="6" t="str"/>
     </x:row>
@@ -931,7 +931,7 @@
       </x:c>
       <x:c r="I21" s="6" t="str"/>
       <x:c r="J21" s="6" t="n">
-        <x:v>7</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K21" s="6" t="str"/>
     </x:row>
@@ -962,7 +962,7 @@
         <x:v>space</x:v>
       </x:c>
       <x:c r="J22" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K22" s="6" t="str"/>
     </x:row>
@@ -993,7 +993,7 @@
         <x:v>evolve</x:v>
       </x:c>
       <x:c r="J23" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K23" s="6" t="str"/>
     </x:row>
@@ -1024,7 +1024,7 @@
         <x:v>obstacles</x:v>
       </x:c>
       <x:c r="J24" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K24" s="6" t="str"/>
     </x:row>
@@ -1053,7 +1053,7 @@
       </x:c>
       <x:c r="I25" s="6" t="str"/>
       <x:c r="J25" s="6" t="n">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K25" s="6" t="str"/>
     </x:row>
@@ -1082,7 +1082,7 @@
       </x:c>
       <x:c r="I26" s="6" t="str"/>
       <x:c r="J26" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K26" s="6" t="str"/>
     </x:row>
@@ -1111,7 +1111,7 @@
       </x:c>
       <x:c r="I27" s="6" t="str"/>
       <x:c r="J27" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K27" s="6" t="str"/>
     </x:row>
@@ -1140,7 +1140,7 @@
       </x:c>
       <x:c r="I28" s="6" t="str"/>
       <x:c r="J28" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K28" s="6" t="str"/>
     </x:row>
@@ -1169,7 +1169,7 @@
       </x:c>
       <x:c r="I29" s="6" t="str"/>
       <x:c r="J29" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K29" s="6" t="str"/>
     </x:row>
@@ -1200,7 +1200,7 @@
         <x:v>obstacles</x:v>
       </x:c>
       <x:c r="J30" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K30" s="6" t="str"/>
     </x:row>
@@ -1229,7 +1229,7 @@
       </x:c>
       <x:c r="I31" s="6" t="str"/>
       <x:c r="J31" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K31" s="6" t="str"/>
     </x:row>
@@ -1258,7 +1258,7 @@
       </x:c>
       <x:c r="I32" s="6" t="str"/>
       <x:c r="J32" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K32" s="6" t="str">
         <x:v>F02</x:v>
@@ -1289,7 +1289,7 @@
       </x:c>
       <x:c r="I33" s="6" t="str"/>
       <x:c r="J33" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K33" s="6" t="str">
         <x:v>F01</x:v>
@@ -1320,7 +1320,7 @@
       </x:c>
       <x:c r="I34" s="6" t="str"/>
       <x:c r="J34" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K34" s="6" t="str"/>
     </x:row>
@@ -1349,7 +1349,7 @@
       </x:c>
       <x:c r="I35" s="6" t="str"/>
       <x:c r="J35" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K35" s="6" t="str"/>
     </x:row>
@@ -1378,7 +1378,7 @@
       </x:c>
       <x:c r="I36" s="6" t="str"/>
       <x:c r="J36" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K36" s="6" t="str"/>
     </x:row>
@@ -1407,7 +1407,7 @@
       </x:c>
       <x:c r="I37" s="6" t="str"/>
       <x:c r="J37" s="6" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K37" s="6" t="str"/>
     </x:row>

--- a/design/tables/ChallengePerk.xlsx
+++ b/design/tables/ChallengePerk.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengePerk" sheetId="1" r:id="R061e13ea59494f04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengePerk" sheetId="1" r:id="R3d15516357554d62"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -278,6 +278,7 @@
     <x:col min="9" max="9" width="23" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="23" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="23" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="23.75" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="40" customHeight="1">
@@ -314,6 +315,9 @@
       <x:c r="K1" s="5" t="str">
         <x:v>互斥效果编号</x:v>
       </x:c>
+      <x:c r="L1" s="5" t="str">
+        <x:v>可重复选择</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="40" customHeight="1">
       <x:c r="A2" s="5" t="str">
@@ -349,6 +353,9 @@
       <x:c r="K2" s="5" t="str">
         <x:v>client</x:v>
       </x:c>
+      <x:c r="L2" s="5" t="str">
+        <x:v>client</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="40" customHeight="1">
       <x:c r="A3" s="5" t="str">
@@ -384,6 +391,9 @@
       <x:c r="K3" s="5" t="str">
         <x:v>string</x:v>
       </x:c>
+      <x:c r="L3" s="5" t="str">
+        <x:v>int</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="40" customHeight="1">
       <x:c r="A4" s="5" t="str">
@@ -419,6 +429,9 @@
       <x:c r="K4" s="5" t="str">
         <x:v>互斥效果编号</x:v>
       </x:c>
+      <x:c r="L4" s="5" t="str">
+        <x:v>可重复选择</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="40" customHeight="1">
       <x:c r="A5" s="5" t="str">
@@ -454,6 +467,9 @@
       <x:c r="K5" s="5" t="str">
         <x:v>exclusive</x:v>
       </x:c>
+      <x:c r="L5" s="5" t="str">
+        <x:v>repeatable</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="60" customHeight="1">
       <x:c r="A6" s="6" t="n">
@@ -478,13 +494,16 @@
         <x:v>perk_S01</x:v>
       </x:c>
       <x:c r="H6" s="6" t="str">
-        <x:v>{"every":2,"shots":3,"ratio":0.7}</x:v>
+        <x:v>{"every":2,"shots":3,"ratio":0.48}</x:v>
       </x:c>
       <x:c r="I6" s="6" t="str"/>
       <x:c r="J6" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K6" s="6" t="str"/>
+      <x:c r="L6" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="60" customHeight="1">
       <x:c r="A7" s="6" t="n">
@@ -509,13 +528,16 @@
         <x:v>perk_S02</x:v>
       </x:c>
       <x:c r="H7" s="6" t="str">
-        <x:v>{"radius":80,"count":2,"seconds":1.5}</x:v>
+        <x:v>{"radius":70,"count":2,"seconds":1.1}</x:v>
       </x:c>
       <x:c r="I7" s="6" t="str"/>
       <x:c r="J7" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K7" s="6" t="str"/>
+      <x:c r="L7" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="60" customHeight="1">
       <x:c r="A8" s="6" t="n">
@@ -540,13 +562,16 @@
         <x:v>perk_S03</x:v>
       </x:c>
       <x:c r="H8" s="6" t="str">
-        <x:v>{"every":2,"delay":0.22,"ratio":0.9,"radiusRatio":1.45}</x:v>
+        <x:v>{"every":2,"delay":0.22,"ratio":0.5,"radiusRatio":1.25}</x:v>
       </x:c>
       <x:c r="I8" s="6" t="str"/>
       <x:c r="J8" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K8" s="6" t="str"/>
+      <x:c r="L8" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="60" customHeight="1">
       <x:c r="A9" s="6" t="n">
@@ -571,13 +596,16 @@
         <x:v>perk_S04</x:v>
       </x:c>
       <x:c r="H9" s="6" t="str">
-        <x:v>{"ratio":0.35}</x:v>
+        <x:v>{"ratio":0.2}</x:v>
       </x:c>
       <x:c r="I9" s="6" t="str"/>
       <x:c r="J9" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K9" s="6" t="str"/>
+      <x:c r="L9" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="60" customHeight="1">
       <x:c r="A10" s="6" t="n">
@@ -602,13 +630,16 @@
         <x:v>perk_S05</x:v>
       </x:c>
       <x:c r="H10" s="6" t="str">
-        <x:v>{"every":2,"ratio":0.8,"count":5}</x:v>
+        <x:v>{"every":2,"ratio":0.5,"count":4}</x:v>
       </x:c>
       <x:c r="I10" s="6" t="str"/>
       <x:c r="J10" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K10" s="6" t="str"/>
+      <x:c r="L10" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="60" customHeight="1">
       <x:c r="A11" s="6" t="n">
@@ -633,13 +664,16 @@
         <x:v>perk_S06</x:v>
       </x:c>
       <x:c r="H11" s="6" t="str">
-        <x:v>{"radius":72,"ratio":2.1,"count":8}</x:v>
+        <x:v>{"radius":64,"ratio":1.35,"count":6}</x:v>
       </x:c>
       <x:c r="I11" s="6" t="str"/>
       <x:c r="J11" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K11" s="6" t="str"/>
+      <x:c r="L11" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="60" customHeight="1">
       <x:c r="A12" s="6" t="n">
@@ -664,13 +698,16 @@
         <x:v>perk_S07</x:v>
       </x:c>
       <x:c r="H12" s="6" t="str">
-        <x:v>{"radius":100,"count":2,"seconds":2,"generations":3}</x:v>
+        <x:v>{"radius":85,"count":2,"seconds":1.5,"generations":2}</x:v>
       </x:c>
       <x:c r="I12" s="6" t="str"/>
       <x:c r="J12" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K12" s="6" t="str"/>
+      <x:c r="L12" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="60" customHeight="1">
       <x:c r="A13" s="6" t="n">
@@ -695,13 +732,16 @@
         <x:v>perk_S08</x:v>
       </x:c>
       <x:c r="H13" s="6" t="str">
-        <x:v>{"radius":80,"ratio":0.8}</x:v>
+        <x:v>{"radius":70,"ratio":0.5}</x:v>
       </x:c>
       <x:c r="I13" s="6" t="str"/>
       <x:c r="J13" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K13" s="6" t="str"/>
+      <x:c r="L13" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="60" customHeight="1">
       <x:c r="A14" s="6" t="n">
@@ -724,13 +764,16 @@
         <x:v>perk_G01</x:v>
       </x:c>
       <x:c r="H14" s="6" t="str">
-        <x:v>{"seconds":6,"rate":-0.35}</x:v>
+        <x:v>{"seconds":5,"rate":-0.22}</x:v>
       </x:c>
       <x:c r="I14" s="6" t="str"/>
       <x:c r="J14" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K14" s="6" t="str"/>
+      <x:c r="L14" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="60" customHeight="1">
       <x:c r="A15" s="6" t="n">
@@ -753,13 +796,16 @@
         <x:v>perk_G02</x:v>
       </x:c>
       <x:c r="H15" s="6" t="str">
-        <x:v>{"radius":90,"damage":0.25}</x:v>
+        <x:v>{"radius":90,"damage":0.14}</x:v>
       </x:c>
       <x:c r="I15" s="6" t="str"/>
       <x:c r="J15" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K15" s="6" t="str"/>
+      <x:c r="L15" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="60" customHeight="1">
       <x:c r="A16" s="6" t="n">
@@ -782,13 +828,16 @@
         <x:v>perk_G03</x:v>
       </x:c>
       <x:c r="H16" s="6" t="str">
-        <x:v>{"radius":90,"damage":0.5,"range":-0.1}</x:v>
+        <x:v>{"radius":90,"damage":0.28,"range":-0.1}</x:v>
       </x:c>
       <x:c r="I16" s="6" t="str"/>
       <x:c r="J16" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K16" s="6" t="str"/>
+      <x:c r="L16" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="60" customHeight="1">
       <x:c r="A17" s="6" t="n">
@@ -811,13 +860,16 @@
         <x:v>perk_G04</x:v>
       </x:c>
       <x:c r="H17" s="6" t="str">
-        <x:v>{"step":100,"damage":0.02,"cap":0.2}</x:v>
+        <x:v>{"step":100,"damage":0.012,"cap":0.12}</x:v>
       </x:c>
       <x:c r="I17" s="6" t="str"/>
       <x:c r="J17" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K17" s="6" t="str"/>
+      <x:c r="L17" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="60" customHeight="1">
       <x:c r="A18" s="6" t="n">
@@ -840,13 +892,16 @@
         <x:v>perk_G05</x:v>
       </x:c>
       <x:c r="H18" s="6" t="str">
-        <x:v>{"damage":0.25,"range":0.15}</x:v>
+        <x:v>{"damage":0.14,"range":0.08}</x:v>
       </x:c>
       <x:c r="I18" s="6" t="str"/>
       <x:c r="J18" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K18" s="6" t="str"/>
+      <x:c r="L18" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="60" customHeight="1">
       <x:c r="A19" s="6" t="n">
@@ -869,13 +924,16 @@
         <x:v>perk_G06</x:v>
       </x:c>
       <x:c r="H19" s="6" t="str">
-        <x:v>{"damage":0.35}</x:v>
+        <x:v>{"damage":0.18}</x:v>
       </x:c>
       <x:c r="I19" s="6" t="str"/>
       <x:c r="J19" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K19" s="6" t="str"/>
+      <x:c r="L19" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="60" customHeight="1">
       <x:c r="A20" s="6" t="n">
@@ -898,13 +956,16 @@
         <x:v>perk_E01</x:v>
       </x:c>
       <x:c r="H20" s="6" t="str">
-        <x:v>{"coins":200}</x:v>
+        <x:v>{"coins":90}</x:v>
       </x:c>
       <x:c r="I20" s="6" t="str"/>
       <x:c r="J20" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K20" s="6" t="str"/>
+      <x:c r="L20" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="60" customHeight="1">
       <x:c r="A21" s="6" t="n">
@@ -927,13 +988,16 @@
         <x:v>perk_E02</x:v>
       </x:c>
       <x:c r="H21" s="6" t="str">
-        <x:v>{"waves":5,"ratio":0.15,"cap":75}</x:v>
+        <x:v>{"waves":5,"ratio":0.08,"cap":40}</x:v>
       </x:c>
       <x:c r="I21" s="6" t="str"/>
       <x:c r="J21" s="6" t="n">
-        <x:v>14</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K21" s="6" t="str"/>
+      <x:c r="L21" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="60" customHeight="1">
       <x:c r="A22" s="6" t="n">
@@ -956,15 +1020,18 @@
         <x:v>perk_E03</x:v>
       </x:c>
       <x:c r="H22" s="6" t="str">
-        <x:v>{"charges":3}</x:v>
+        <x:v>{"charges":2}</x:v>
       </x:c>
       <x:c r="I22" s="6" t="str">
         <x:v>space</x:v>
       </x:c>
       <x:c r="J22" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K22" s="6" t="str"/>
+      <x:c r="L22" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="60" customHeight="1">
       <x:c r="A23" s="6" t="n">
@@ -987,15 +1054,18 @@
         <x:v>perk_E04</x:v>
       </x:c>
       <x:c r="H23" s="6" t="str">
-        <x:v>{"charges":2}</x:v>
+        <x:v>{"charges":1}</x:v>
       </x:c>
       <x:c r="I23" s="6" t="str">
         <x:v>evolve</x:v>
       </x:c>
       <x:c r="J23" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K23" s="6" t="str"/>
+      <x:c r="L23" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="60" customHeight="1">
       <x:c r="A24" s="6" t="n">
@@ -1018,15 +1088,18 @@
         <x:v>perk_E05</x:v>
       </x:c>
       <x:c r="H24" s="6" t="str">
-        <x:v>{"coins":60,"reward":30}</x:v>
+        <x:v>{"coins":40,"reward":16}</x:v>
       </x:c>
       <x:c r="I24" s="6" t="str">
         <x:v>obstacles</x:v>
       </x:c>
       <x:c r="J24" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K24" s="6" t="str"/>
+      <x:c r="L24" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="60" customHeight="1">
       <x:c r="A25" s="6" t="n">
@@ -1049,13 +1122,16 @@
         <x:v>perk_E06</x:v>
       </x:c>
       <x:c r="H25" s="6" t="str">
-        <x:v>{"ratio":0.25}</x:v>
+        <x:v>{"ratio":0.12}</x:v>
       </x:c>
       <x:c r="I25" s="6" t="str"/>
       <x:c r="J25" s="6" t="n">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K25" s="6" t="str"/>
+      <x:c r="L25" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="60" customHeight="1">
       <x:c r="A26" s="6" t="n">
@@ -1078,13 +1154,16 @@
         <x:v>perk_X01</x:v>
       </x:c>
       <x:c r="H26" s="6" t="str">
-        <x:v>{"progress":0.3}</x:v>
+        <x:v>{"progress":0.2}</x:v>
       </x:c>
       <x:c r="I26" s="6" t="str"/>
       <x:c r="J26" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K26" s="6" t="str"/>
+      <x:c r="L26" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="60" customHeight="1">
       <x:c r="A27" s="6" t="n">
@@ -1107,13 +1186,16 @@
         <x:v>perk_X02</x:v>
       </x:c>
       <x:c r="H27" s="6" t="str">
-        <x:v>{"shield":2}</x:v>
+        <x:v>{"shield":1}</x:v>
       </x:c>
       <x:c r="I27" s="6" t="str"/>
       <x:c r="J27" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K27" s="6" t="str"/>
+      <x:c r="L27" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="60" customHeight="1">
       <x:c r="A28" s="6" t="n">
@@ -1136,13 +1218,16 @@
         <x:v>perk_X03</x:v>
       </x:c>
       <x:c r="H28" s="6" t="str">
-        <x:v>{"count":3,"progress":0.8,"ratio":0.4,"seconds":2}</x:v>
+        <x:v>{"count":2,"progress":0.8,"ratio":0.55,"seconds":2}</x:v>
       </x:c>
       <x:c r="I28" s="6" t="str"/>
       <x:c r="J28" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K28" s="6" t="str"/>
+      <x:c r="L28" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="60" customHeight="1">
       <x:c r="A29" s="6" t="n">
@@ -1165,13 +1250,16 @@
         <x:v>perk_X04</x:v>
       </x:c>
       <x:c r="H29" s="6" t="str">
-        <x:v>{"coins":100,"rate":-0.25,"seconds":4}</x:v>
+        <x:v>{"coins":120,"rate":-0.18,"seconds":3}</x:v>
       </x:c>
       <x:c r="I29" s="6" t="str"/>
       <x:c r="J29" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K29" s="6" t="str"/>
+      <x:c r="L29" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="60" customHeight="1">
       <x:c r="A30" s="6" t="n">
@@ -1194,15 +1282,18 @@
         <x:v>perk_X05</x:v>
       </x:c>
       <x:c r="H30" s="6" t="str">
-        <x:v>{"radius":100,"ratio":0.35}</x:v>
+        <x:v>{"radius":90,"ratio":0.2}</x:v>
       </x:c>
       <x:c r="I30" s="6" t="str">
         <x:v>obstacles</x:v>
       </x:c>
       <x:c r="J30" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K30" s="6" t="str"/>
+      <x:c r="L30" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="60" customHeight="1">
       <x:c r="A31" s="6" t="n">
@@ -1225,13 +1316,16 @@
         <x:v>perk_X06</x:v>
       </x:c>
       <x:c r="H31" s="6" t="str">
-        <x:v>{"damage":0.4}</x:v>
+        <x:v>{"damage":0.25}</x:v>
       </x:c>
       <x:c r="I31" s="6" t="str"/>
       <x:c r="J31" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K31" s="6" t="str"/>
+      <x:c r="L31" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="60" customHeight="1">
       <x:c r="A32" s="6" t="n">
@@ -1254,14 +1348,17 @@
         <x:v>perk_F01</x:v>
       </x:c>
       <x:c r="H32" s="6" t="str">
-        <x:v>{"damage":0.8,"range":0.15,"rate":0.2,"scale":1.35}</x:v>
+        <x:v>{"damage":0.45,"range":0.08,"rate":0.12,"scale":1.35}</x:v>
       </x:c>
       <x:c r="I32" s="6" t="str"/>
       <x:c r="J32" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K32" s="6" t="str">
         <x:v>F02</x:v>
+      </x:c>
+      <x:c r="L32" s="6" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="60" customHeight="1">
@@ -1285,14 +1382,17 @@
         <x:v>perk_F02</x:v>
       </x:c>
       <x:c r="H33" s="6" t="str">
-        <x:v>{"rate":-0.25,"damage":-0.1,"scale":0.8}</x:v>
+        <x:v>{"rate":-0.18,"damage":-0.1,"scale":0.8}</x:v>
       </x:c>
       <x:c r="I33" s="6" t="str"/>
       <x:c r="J33" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K33" s="6" t="str">
         <x:v>F01</x:v>
+      </x:c>
+      <x:c r="L33" s="6" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="60" customHeight="1">
@@ -1316,13 +1416,16 @@
         <x:v>perk_F03</x:v>
       </x:c>
       <x:c r="H34" s="6" t="str">
-        <x:v>{"every":12,"limit":3,"coins":20,"damage":100,"radius":80,"ratio":0.4,"seconds":2}</x:v>
+        <x:v>{"every":16,"limit":2,"coins":8,"damage":65,"radius":70,"ratio":0.55,"seconds":2}</x:v>
       </x:c>
       <x:c r="I34" s="6" t="str"/>
       <x:c r="J34" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K34" s="6" t="str"/>
+      <x:c r="L34" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="60" customHeight="1">
       <x:c r="A35" s="6" t="n">
@@ -1345,13 +1448,16 @@
         <x:v>perk_F04</x:v>
       </x:c>
       <x:c r="H35" s="6" t="str">
-        <x:v>{"every":24,"damage":100,"count":8,"cooldown":8,"speed":240,"seconds":6,"radius":24}</x:v>
+        <x:v>{"every":30,"damage":70,"count":6,"cooldown":10,"speed":240,"seconds":6,"radius":24}</x:v>
       </x:c>
       <x:c r="I35" s="6" t="str"/>
       <x:c r="J35" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K35" s="6" t="str"/>
+      <x:c r="L35" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="60" customHeight="1">
       <x:c r="A36" s="6" t="n">
@@ -1374,13 +1480,16 @@
         <x:v>perk_F05</x:v>
       </x:c>
       <x:c r="H36" s="6" t="str">
-        <x:v>{"interval":10,"count":3,"delay":0.6,"radius":40,"damage":80}</x:v>
+        <x:v>{"interval":12,"count":2,"delay":0.6,"radius":36,"damage":55}</x:v>
       </x:c>
       <x:c r="I36" s="6" t="str"/>
       <x:c r="J36" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K36" s="6" t="str"/>
+      <x:c r="L36" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="60" customHeight="1">
       <x:c r="A37" s="6" t="n">
@@ -1403,13 +1512,112 @@
         <x:v>perk_F06</x:v>
       </x:c>
       <x:c r="H37" s="6" t="str">
-        <x:v>{"hp":2,"reward":4}</x:v>
+        <x:v>{"hp":2,"reward":3}</x:v>
       </x:c>
       <x:c r="I37" s="6" t="str"/>
       <x:c r="J37" s="6" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K37" s="6" t="str"/>
+      <x:c r="L37" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="6" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B38" s="6" t="str">
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="C38" s="6" t="str">
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="D38" s="6" t="str"/>
+      <x:c r="E38" s="6" t="str">
+        <x:v>perk.R01.name</x:v>
+      </x:c>
+      <x:c r="F38" s="6" t="str">
+        <x:v>perk.R01.desc</x:v>
+      </x:c>
+      <x:c r="G38" s="6" t="str">
+        <x:v>perk_R01</x:v>
+      </x:c>
+      <x:c r="H38" s="6" t="str">
+        <x:v>{"coins":40}</x:v>
+      </x:c>
+      <x:c r="I38" s="6" t="str"/>
+      <x:c r="J38" s="6" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K38" s="6" t="str"/>
+      <x:c r="L38" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="6" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B39" s="6" t="str">
+        <x:v>R02</x:v>
+      </x:c>
+      <x:c r="C39" s="6" t="str">
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="D39" s="6" t="str"/>
+      <x:c r="E39" s="6" t="str">
+        <x:v>perk.R02.name</x:v>
+      </x:c>
+      <x:c r="F39" s="6" t="str">
+        <x:v>perk.R02.desc</x:v>
+      </x:c>
+      <x:c r="G39" s="6" t="str">
+        <x:v>perk_R02</x:v>
+      </x:c>
+      <x:c r="H39" s="6" t="str">
+        <x:v>{"ratio":0.2,"seconds":2}</x:v>
+      </x:c>
+      <x:c r="I39" s="6" t="str"/>
+      <x:c r="J39" s="6" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K39" s="6" t="str"/>
+      <x:c r="L39" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="6" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B40" s="6" t="str">
+        <x:v>R03</x:v>
+      </x:c>
+      <x:c r="C40" s="6" t="str">
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="D40" s="6" t="str"/>
+      <x:c r="E40" s="6" t="str">
+        <x:v>perk.R03.name</x:v>
+      </x:c>
+      <x:c r="F40" s="6" t="str">
+        <x:v>perk.R03.desc</x:v>
+      </x:c>
+      <x:c r="G40" s="6" t="str">
+        <x:v>perk_R03</x:v>
+      </x:c>
+      <x:c r="H40" s="6" t="str">
+        <x:v>{"shield":1,"cap":2}</x:v>
+      </x:c>
+      <x:c r="I40" s="6" t="str"/>
+      <x:c r="J40" s="6" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K40" s="6" t="str"/>
+      <x:c r="L40" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
